--- a/demo_gui/1_売上（下書き）.xlsx
+++ b/demo_gui/1_売上（下書き）.xlsx
@@ -134,15 +134,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>

--- a/demo_gui/1_売上（下書き）.xlsx
+++ b/demo_gui/1_売上（下書き）.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">商品</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t xml:space="preserve">みかん</t>
-  </si>
-  <si>
-    <t xml:space="preserve">梨</t>
   </si>
   <si>
     <t xml:space="preserve">ぶどう</t>
@@ -47,11 +44,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,14 +71,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -128,21 +116,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -352,46 +332,40 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="1" t="n">
         <v>1200</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>900</v>
       </c>
     </row>

--- a/demo_gui/1_売上（下書き）.xlsx
+++ b/demo_gui/1_売上（下書き）.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t xml:space="preserve">商品</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t xml:space="preserve">みかん</t>
+  </si>
+  <si>
+    <t xml:space="preserve">梨</t>
   </si>
   <si>
     <t xml:space="preserve">ぶどう</t>
@@ -317,7 +320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -332,40 +335,68 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>800</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>300</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C9" s="1" t="n">
         <v>900</v>
       </c>
     </row>

--- a/demo_gui/1_売上（下書き）.xlsx
+++ b/demo_gui/1_売上（下書き）.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">商品</t>
   </si>
@@ -50,7 +50,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +74,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -119,8 +127,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -320,7 +332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -335,68 +347,42 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>900</v>
       </c>
     </row>
